--- a/cadastros_import_modelo.xlsx
+++ b/cadastros_import_modelo.xlsx
@@ -13,37 +13,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>nome_completo</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>telefone_whatsapp</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>origem</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>igreja_origem</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>bairro</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>observacoes</t>
+          <t>culto</t>
         </is>
       </c>
     </row>
@@ -55,32 +40,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9299999-9999</t>
+          <t>(92) 99999-9999</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Célula</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sede</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Contato via WhatsApp</t>
+          <t>Domingo noite</t>
         </is>
       </c>
     </row>
